--- a/arquivos_originais/incident.xlsx
+++ b/arquivos_originais/incident.xlsx
@@ -164,16 +164,16 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>INC1435010</t>
+          <t>INC1437987</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>ABEND DS - BS - SUSTENTACAO - BVP - SISE-SP - JOB PP_SISE5028_M</t>
+          <t>ABEND DS - BS - SUSTENTACAO - BVP - SISE-SP - JOB PP_SISE1115_D</t>
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>46113.83703703704</v>
+        <v>46118.177881944444</v>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
@@ -182,7 +182,7 @@
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>JOAO VITOR ALTOMAR</t>
+          <t>DIOGO DA FRANCA RODRIGUES</t>
         </is>
       </c>
       <c r="F2" s="10" t="inlineStr">
@@ -192,7 +192,7 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>PP_SISE5028_M</t>
+          <t>PP_SISE1115_D</t>
         </is>
       </c>
       <c r="H2" s="10" t="inlineStr">
@@ -202,7 +202,7 @@
       </c>
       <c r="I2" s="10" t="inlineStr">
         <is>
-          <t>2 - Alto(a)</t>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
